--- a/survey_templates/036_innovation_project_evaluation_form--survey_templates.xlsx
+++ b/survey_templates/036_innovation_project_evaluation_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1110,8 +1110,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'r\\&amp;d',_'label':_'r\\&amp;d'}</t>
+          <t>r\&amp;d</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'R\\&amp;D', 'label': 'R\\&amp;D'}</t>
+          <t>R\&amp;D</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'marketing',_'label':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Marketing', 'label': 'Marketing'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'business_development',_'label':_'business_development'}</t>
+          <t>business_development</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Business Development', 'label': 'Business Development'}</t>
+          <t>Business Development</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'effectiveness',_'label':_'effectiveness'}</t>
+          <t>effectiveness</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Effectiveness', 'label': 'Effectiveness'}</t>
+          <t>Effectiveness</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'efficiency',_'label':_'efficiency'}</t>
+          <t>efficiency</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Efficiency', 'label': 'Efficiency'}</t>
+          <t>Efficiency</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'impact',_'label':_'impact'}</t>
+          <t>impact</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Impact', 'label': 'Impact'}</t>
+          <t>Impact</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'survey',_'label':_'survey'}</t>
+          <t>survey</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Survey', 'label': 'Survey'}</t>
+          <t>Survey</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'interview',_'label':_'interview'}</t>
+          <t>interview</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Interview', 'label': 'Interview'}</t>
+          <t>Interview</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'case_study',_'label':_'case_study'}</t>
+          <t>case_study</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Case Study', 'label': 'Case Study'}</t>
+          <t>Case Study</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'active',_'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Active', 'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'inactive',_'label':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Inactive', 'label': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'on_hold',_'label':_'on_hold'}</t>
+          <t>on_hold</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'On Hold', 'label': 'On Hold'}</t>
+          <t>On Hold</t>
         </is>
       </c>
     </row>
